--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
-  <si>
-    <t>Statement: WorkoutSessionService.updateWorkoutSessionWithExercises(id, data, exercises) – Delegates to workoutSessionRepository.updateWithExercises(). Propagates WorkoutSessionRequiresExercisesError if exercises empty. Propagates NotFoundError if session absent.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="42">
+  <si>
+    <t>Statement: WorkoutSessionService.updateWorkoutSessionWithExercises(id, data, ex)</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id: string, data: UpdateWorkoutSessionInput, exercises: WorkoutSessionExerciseUpdateInput[] (≥1)</t>
+    <t>Input: id, data, ex</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionRepository is accessible</t>
+    <t>repo accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt;  OR  throws WorkoutSessionRequiresExercisesError / NotFoundError</t>
+    <t>Output: session</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: session + exercises fully replaced atomically. On error: no state change.</t>
+    <t>Updated.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,24 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>exercises array</t>
-  </si>
-  <si>
-    <t>length ≥ 1</t>
-  </si>
-  <si>
-    <t>length = 0 (WorkoutSessionRequiresExercisesError)</t>
-  </si>
-  <si>
-    <t>session existence</t>
-  </si>
-  <si>
-    <t>session found</t>
-  </si>
-  <si>
-    <t>session not found (NotFoundError)</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -97,91 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>id exists, valid data, 1 exercise</t>
-  </si>
-  <si>
-    <t>Returns WorkoutSessionWithExercises; updateWithExercises called</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>id exists, valid data, exercises=[]</t>
-  </si>
-  <si>
-    <t>Throws WorkoutSessionRequiresExercisesError</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>"nonexistent-id", valid data, 1 exercise</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>exercises.length</t>
-  </si>
-  <si>
-    <t>exercises=[] → error; exercises=[1] → success</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>exercises.length=0</t>
-  </si>
-  <si>
-    <t>exercises=[], existing session</t>
-  </si>
-  <si>
-    <t>exercises.length=1</t>
-  </si>
-  <si>
-    <t>exercises=[1 item], existing session</t>
-  </si>
-  <si>
-    <t>Returns WorkoutSessionWithExercises</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>Existing id, 1 exercise</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>exercises=[]</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Non-existent session id</t>
+    <t>Update with ex</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -739,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -761,62 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -825,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -837,70 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -921,24 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -949,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -961,53 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1031,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1054,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1074,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1094,19 +861,159 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>34</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1134,16 +1041,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1151,45 +1058,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1198,19 +1105,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="42">
-  <si>
-    <t>Statement: WorkoutSessionService.updateWorkoutSessionWithExercises(id, data, ex)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="81">
+  <si>
+    <t>Statement: WorkoutSessionService.updateWorkoutSessionWithExercises(id, data, exercises) – Updates a workout session and its exercises atomically. Returns the updated WorkoutSessionWithExercises on success. Throws WorkoutSessionRequiresExercisesError if exercises array is empty. Throws NotFoundError if no session exists with the given ID. Throws TransactionError if the DB write fails.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id, data, ex</t>
+    <t>Input: id: string, data: UpdateWorkoutSessionInput, exercises: WorkoutSessionExerciseUpdateInput[]</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>repo accessible</t>
+    <t>A session with the given ID may or may not exist. The exercises array may be empty or contain one or more entries with or without existing session exercise IDs.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: session</t>
+    <t>Output: Promise&lt;WorkoutSessionWithExercises&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Updated.</t>
+    <t>On success: updated WorkoutSessionWithExercises returned reflecting changed session fields and exercise entries. On failure: WorkoutSessionRequiresExercisesError, NotFoundError, or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,39 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Session existence</t>
+  </si>
+  <si>
+    <t>Existing ID + new exercises → full updated session returned</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
+  </si>
+  <si>
+    <t>Exercises array</t>
+  </si>
+  <si>
+    <t>1 or more exercises → session returned with exercises</t>
+  </si>
+  <si>
+    <t>Empty array → WorkoutSessionRequiresExercisesError</t>
+  </si>
+  <si>
+    <t>Exercise entry reuse</t>
+  </si>
+  <si>
+    <t>Existing SE ID provided → entry updated with new sets/reps/weight</t>
+  </si>
+  <si>
+    <t>Database write result</t>
+  </si>
+  <si>
+    <t>Write succeeds → session returned</t>
+  </si>
+  <si>
+    <t>Write fails → TransactionError</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,28 +112,112 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned (toEqual MOCK_SESSION_WITH_EXERCISES), id: SESSION_ID, exercises.length: 1, exercises[0].exerciseId: EXERCISE_ID</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: []</t>
+  </si>
+  <si>
+    <t>throws WorkoutSessionRequiresExercisesError("Requires exercises")</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>id: NONEXISTENT_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Session not found")</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, exercises: [{ id: "se-uuid-001", sets: 4, reps: 8, weight: 90 }]</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned (toEqual updatedMock), exercises[0].sets: 4</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT (DB fails)</t>
+  </si>
+  <si>
+    <t>throws TransactionError("DB error")</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Session ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>Exercises count</t>
+  </si>
+  <si>
+    <t>1 exercise (minimum valid count)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "", data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match), data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>id: "a" (found), data: UPDATE_SESSION_INPUT, exercises: EXERCISE_INPUT</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with id: "a" (toEqual expectedReturn)</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=1)</t>
+  </si>
+  <si>
+    <t>id: SESSION_ID, data: UPDATE_SESSION_INPUT, exercises: [1 exercise]</t>
+  </si>
+  <si>
+    <t>WorkoutSessionWithExercises returned with exercises.length: 1, exercises[0].exerciseId: EXERCISE_ID</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Update with ex</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>BVA-1</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
   </si>
   <si>
     <t>Testing</t>
@@ -133,7 +250,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-06/WSM-07</t>
+    <t>SERV-26</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +797,104 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +903,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +915,104 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +1033,35 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1084,87 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -785,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -798,22 +1188,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1211,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1231,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1251,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1271,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1291,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1311,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1331,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1351,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,39 +1371,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1041,16 +1411,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1058,45 +1428,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B3" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1105,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/workout-session-service/updateWorkoutSessionWithExercises-bbt-form.xlsx
@@ -250,7 +250,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-26</t>
+    <t>SERV-27</t>
   </si>
   <si>
     <t>n/a</t>
